--- a/materialy/karty-poza-kolejka.xlsx
+++ b/materialy/karty-poza-kolejka.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Metodologia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Karty poza kolejka'!$A$1:$K$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Karty poza kolejka'!$A$1:$K$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -662,63 +662,63 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>30714</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Paryż – miasto miłości</t>
+          <t>Rudy kot</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>LEGO Architecture</t>
+          <t>Creator</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>958</v>
+        <v>79</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>339.99</v>
+        <v>16.49</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>karta Piotra</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/30714/</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>21064-1</t>
+          <t>30714-1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>30714</t>
+          <t>30715</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Rudy kot</t>
+          <t>Przyjęcie urodzinowe z uroczymi zwierzątkami</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -730,7 +730,7 @@
         <v>2026</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>16.49</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/30714/</t>
+          <t>/zestaw/30715/</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -757,31 +757,31 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>30714-1</t>
+          <t>30715-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>30715</t>
+          <t>30722</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Przyjęcie urodzinowe z uroczymi zwierzątkami</t>
+          <t>Domek króliczka w ogrodzie</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Creator</t>
+          <t>Friends</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>16.49</v>
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>/zestaw/30715/</t>
+          <t>/zestaw/30722/</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -808,31 +808,31 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>30715-1</t>
+          <t>30722-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>30722</t>
+          <t>30723</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Domek króliczka w ogrodzie</t>
+          <t>Samochód ninja Cole’a</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>Ninjago</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>16.49</v>
@@ -844,7 +844,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/30722/</t>
+          <t>/zestaw/30723/</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -859,31 +859,31 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>30722-1</t>
+          <t>30723-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>30724</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Samochód ninja Cole’a</t>
+          <t>Gabinet Dumbledore’a z Harrym Potterem</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Ninjago</t>
+          <t>Harry Potter</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>16.49</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>/zestaw/30723/</t>
+          <t>/zestaw/30724/</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -910,31 +910,31 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>30723-1</t>
+          <t>30724-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Gabinet Dumbledore’a z Harrym Potterem</t>
+          <t>Minimodel Brzeszczota</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Harry Potter</t>
+          <t>Star Wars</t>
         </is>
       </c>
       <c r="D9" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>16.49</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/30724/</t>
+          <t>/zestaw/30728/</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -961,31 +961,31 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>30724-1</t>
+          <t>30728-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>30735</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Minimodel Brzeszczota</t>
+          <t>Hot Rod</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Star Wars</t>
+          <t>Technic</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>16.49</v>
@@ -997,7 +997,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>/zestaw/30728/</t>
+          <t>/zestaw/30735/</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1012,43 +1012,41 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>30728-1</t>
+          <t>30735-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>30735</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Hot Rod</t>
+          <t>I love Billund</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Technic</t>
+          <t>Ekskluzywne i promocyjne</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>16.49</v>
-      </c>
+        <v>1404</v>
+      </c>
+      <c r="F11" s="12" t="n"/>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>karta Piotra</t>
+          <t>brak - GWP lub cena nieogloszona</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/30735/</t>
+          <t>/zestaw/40507/</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1063,538 +1061,538 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>30735-1</t>
+          <t>40507-1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Japoński krajobraz z kwitnącą wiśnią</t>
+          <t>The Mandalorian and Grogu: Sojusznicy i złoczyńcy</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>LEGO Art</t>
+          <t>BrickHeadz</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1892</v>
+        <v>661</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>519.99</v>
+        <v>169.99</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>rejestr RRP</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/40856/</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>31218-1</t>
+          <t>40856-1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>31220</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Claude Monet – Most nad stawem z liliami wodnymi</t>
+          <t>Wielkanocne dekoracje</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>LEGO Art</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>3179</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>869.99</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="F13" s="12" t="n"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>brak - GWP lub cena nieogloszona</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>/zestaw/40890/</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>31220-1</t>
+          <t>40890-1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>40891</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>I love Billund</t>
+          <t>Stranger Things: Stacja radiowa WSQK</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>LEGO House</t>
+          <t>Icons</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1404</v>
-      </c>
-      <c r="F14" s="6" t="n"/>
+        <v>234</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>109.99</v>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>brak - GWP lub cena nieogloszona</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>katalog</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/40891/</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>wycofany (EOL)</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>40507-1</t>
+          <t>40891-1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>40893</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>The Mandalorian and Grogu: Sojusznicy i złoczyńcy</t>
+          <t>Grond</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>BrickHeadz</t>
+          <t>Icons</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>661</v>
+        <v>307</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>169.99</v>
+        <v>124.99</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>rejestr RRP</t>
+          <t>katalog</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/40856/</t>
+          <t>/zestaw/40893/</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>brak ceny katalogowej</t>
+          <t>wycofany (EOL)</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
+          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>40856-1</t>
+          <t>40893-1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>40894</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Wielkanocne dekoracje</t>
+          <t>Kierownica Koenigsegg Sadair's Spear</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Technic</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>312</v>
-      </c>
-      <c r="F16" s="6" t="n"/>
+        <v>228</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>104.99</v>
+      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>brak - GWP lub cena nieogloszona</t>
+          <t>katalog</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>/zestaw/40890/</t>
+          <t>/zestaw/40894/</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>brak ceny katalogowej</t>
+          <t>wycofany (EOL)</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
+          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>40890-1</t>
+          <t>40894-1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>40891</t>
+          <t>40897</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Stranger Things: Stacja radiowa WSQK</t>
+          <t>Miecz świetlny Dartha Vadera</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Icons</t>
+          <t>Star Wars</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>234</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>109.99</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="F17" s="12" t="n"/>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>katalog</t>
+          <t>brak - GWP lub cena nieogloszona</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/40891/</t>
+          <t>/zestaw/40897/</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>wycofany (EOL)</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>40891-1</t>
+          <t>40897-1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>40892</t>
+          <t>40901</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Kolekcja odznak z regionu Kanto</t>
+          <t>Przekąski Ministerskie i Prorok Codzienny – stoiska</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>LEGO Pokémon</t>
+          <t>Harry Potter</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>312</v>
+        <v>152</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>129.99</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>karta Piotra</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>katalog</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/40901/</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>wycofany (EOL)</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>40892-1</t>
+          <t>40901-1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>40893</t>
+          <t>40902</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Grond</t>
+          <t>Hołd dla Leonarda da Vinci</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Icons</t>
+          <t>Ekskluzywne i promocyjne</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>307</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>124.99</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="F19" s="12" t="n"/>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>katalog</t>
+          <t>brak - GWP lub cena nieogloszona</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/40893/</t>
+          <t>/zestaw/40902/</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>wycofany (EOL)</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>40893-1</t>
+          <t>40902-1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>40894</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Kierownica Koenigsegg Sadair's Spear</t>
+          <t>Mistrz Rzucania Mięsem i Podniebna - figurki</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Technic</t>
+          <t>BrickHeadz</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>104.99</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>katalog</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>karta Piotra</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/40910/</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>wycofany (EOL)</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>40894-1</t>
+          <t>40910-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>40897</t>
+          <t>40912</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Miecz świetlny Dartha Vadera</t>
+          <t>Wąż morski</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>LEGO Star Wars</t>
+          <t>Ideas</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>174</v>
-      </c>
-      <c r="F21" s="12" t="n"/>
+        <v>241</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>104.99</v>
+      </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>brak - GWP lub cena nieogloszona</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>karta Piotra</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>/zestaw/40912/</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>wycofany (EOL)</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>40897-1</t>
+          <t>40912-1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>40901</t>
+          <t>40913</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Przekąski Ministerskie i Prorok Codzienny – stoiska</t>
+          <t>Zabytkowy samochód z parady</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Harry Potter</t>
+          <t>Icons</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>81.98999999999999</v>
+        <v>109.99</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -1603,7 +1601,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>/zestaw/40901/</t>
+          <t>/zestaw/40913/</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1618,245 +1616,243 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>40901-1</t>
+          <t>40913-1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>40902</t>
+          <t>40916</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Hołd dla Leonarda da Vinci</t>
+          <t>Kwiatowa ramka na zdjęcia</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>LEGO Inne</t>
+          <t>Botanicals</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>251</v>
-      </c>
-      <c r="F23" s="12" t="n"/>
+        <v>310</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>109.99</v>
+      </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>brak - GWP lub cena nieogloszona</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>karta Piotra</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>/zestaw/40916/</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>40902-1</t>
+          <t>40916-1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>40906</t>
+          <t>40917</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Restauracje świata: Japonia</t>
+          <t>Mroczny Miecz</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>LEGO Inne</t>
+          <t>Star Wars</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>84.98999999999999</v>
+        <v>124.99</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>karta Piotra</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>katalog</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/40917/</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>wycofany (EOL)</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>40906-1</t>
+          <t>40917-1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>40907</t>
+          <t>40922</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Restauracje świata: Meksyk</t>
+          <t>Lilo i Stitch: Andzia</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>LEGO Inne</t>
+          <t>BrickHeadz</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>326</v>
+        <v>133</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>84.98999999999999</v>
+        <v>54.99</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>karta Piotra</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>rejestr RRP</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>/zestaw/40922/</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>40907-1</t>
+          <t>40922-1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>40952</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Restauracje świata: Grecja</t>
+          <t>Zamek LEGOLAND</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>LEGO Inne</t>
+          <t>Ekskluzywne i promocyjne</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>254</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>81.98999999999999</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="F26" s="6" t="n"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>karta Piotra</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>brak - GWP lub cena nieogloszona</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/40952/</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>40908-1</t>
+          <t>40952-1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>40910</t>
+          <t>66813</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Mistrz Rzucania Mięsem i Podniebna - figurki</t>
+          <t>Seria 28 – Zwierzęta – sześciopak</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>BrickHeadz</t>
+          <t>Minifigurki</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
         <v>2026</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>288</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>84.98999999999999</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F27" s="12" t="n"/>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>karta Piotra</t>
+          <t>brak - GWP lub cena nieogloszona</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/40910/</t>
+          <t>/zestaw/66813/</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
@@ -1871,340 +1867,320 @@
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>40910-1</t>
+          <t>66813-1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>72050</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Małe Centrum Pokémonów</t>
+          <t>Mario Kart - Luigi i Mach 8</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>LEGO Pokémon</t>
+          <t>Super Mario</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
         <v>2026</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>233</v>
+        <v>2234</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>84.98999999999999</v>
+        <v>779.99</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>karta Piotra</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/72050/</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
+          <t>brak ceny katalogowej</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
+          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>40911-1</t>
+          <t>72050-1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Wąż morski</t>
+          <t>Mario wskakujący do rury</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Ideas</t>
+          <t>Super Mario</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>241</v>
+        <v>61</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>104.99</v>
+        <v>41.99</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>karta Piotra</t>
+          <t>rejestr RRP</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>/zestaw/40912/</t>
+          <t>/zestaw/72052/</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>wycofany (EOL)</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
-        </is>
-      </c>
+          <t>rocznik 2027</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr"/>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>40912-1</t>
+          <t>72052-1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>40913</t>
+          <t>72054</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Zabytkowy samochód z parady</t>
+          <t>Mario Kart™ – wyścigi z Mario</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Icons</t>
+          <t>Super Mario</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>243</v>
+        <v>84</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>109.99</v>
+        <v>62.99</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>katalog</t>
+          <t>rejestr RRP</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>/zestaw/40913/</t>
+          <t>/zestaw/72054/</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>wycofany (EOL)</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
-        </is>
-      </c>
+          <t>rocznik 2027</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>40913-1</t>
+          <t>72054-1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>40916</t>
+          <t>72055</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Kwiatowa ramka na zdjęcia</t>
+          <t>Przygody Mario na plaży</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Botanicals</t>
+          <t>Super Mario</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>310</v>
+        <v>196</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>109.99</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>karta Piotra</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>rejestr RRP</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>/zestaw/72055/</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>brak ceny katalogowej</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
+          <t>rocznik 2027</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr"/>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>40916-1</t>
+          <t>72055-1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>72056</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Mroczny Miecz</t>
+          <t>Mario Kart™ – Luigi i Bowser Jr. na wyścigu</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Star Wars</t>
+          <t>Super Mario</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>278</v>
+        <v>104</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>124.99</v>
+        <v>126.99</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>katalog</t>
+          <t>rejestr RRP</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>/zestaw/40917/</t>
+          <t>/zestaw/72056/</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>wycofany (EOL)</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>decyzja: czy opisujemy zestawy juz wycofane</t>
-        </is>
-      </c>
+          <t>rocznik 2027</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>40917-1</t>
+          <t>72056-1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>40921</t>
+          <t>72057</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Powiększona minifigurka niebieskiego astronauty</t>
+          <t>Yoshi w domu Mario</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>LEGO Minifigurki</t>
+          <t>Super Mario</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>793</v>
+        <v>147</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>249.99</v>
+        <v>174.99</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
           <t>rejestr RRP</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>/zestaw/72057/</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
+          <t>rocznik 2027</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr"/>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>40921-1</t>
+          <t>72057-1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>72058</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Lilo i Stitch: Andzia</t>
+          <t>Mario Kart™ – Bowser i waleczny wyścig</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>BrickHeadz</t>
+          <t>Super Mario</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>133</v>
+        <v>409</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>54.99</v>
+        <v>259.99</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
@@ -2213,1427 +2189,188 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>/zestaw/40922/</t>
+          <t>/zestaw/72058/</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>brak ceny katalogowej</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
+          <t>rocznik 2027</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>40922-1</t>
+          <t>72058-1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>40952</t>
+          <t>72060</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Zamek LEGOLAND</t>
+          <t>Fire Mario i Bowser na zamku</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>LEGO LEGOLAND</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="n"/>
+          <t>Super Mario</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>2027</v>
+      </c>
       <c r="E35" s="11" t="n">
-        <v>613</v>
-      </c>
-      <c r="F35" s="12" t="n"/>
+        <v>850</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>429.99</v>
+      </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>brak - GWP lub cena nieogloszona</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
+          <t>rejestr RRP</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>/zestaw/72060/</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
+          <t>rocznik 2027</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr"/>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>40952-1</t>
+          <t>72060-1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>40955</t>
+          <t>72061</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Kontenerowiec z Napędem Dual-Fuel Maersk</t>
+          <t>Fire Luigi kontra Koopa Troopa – bitwa</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>LEGO Inne</t>
+          <t>Super Mario</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1516</v>
+        <v>241</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>649.99</v>
+        <v>126.99</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>rejestr RRP</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>/zestaw/72061/</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
+          <t>rocznik 2027</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>40955-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>43011</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Lionel Messi – piłkarskie momenty</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>43011-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>43012</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Cristiano Ronaldo – piłkarskie momenty</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>490</v>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>43012-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>43013</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Kylian Mbappé – piłkarskie momenty</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>490</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>43013-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>43014</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Kask Charles Leclerc Scuderia Ferrari HP</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>886</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>379.99</v>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>43014-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>43015</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Lionel Messi – piłkarska legenda</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>958</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>339.99</v>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>43015-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>43016</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Cristiano Ronaldo – piłkarska legenda</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>854</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>339.99</v>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>43016-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>43019</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>Piłka nożna</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>1498</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>519.99</v>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>43019-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>43022</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Kask Lewis Hamilton Scuderia Ferrari HP</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>884</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>379.99</v>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>43022-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>43027</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Vini Jr. – piłkarskie momenty</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>510</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>43027-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>43032</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Oficjalne logo FIFA World Cup 2026™</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>298</v>
-      </c>
-      <c r="F46" s="6" t="n">
-        <v>104.99</v>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>43032-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>43033</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Koszulka piłkarska reprezentacji USA 2026</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Editions</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>167</v>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>104.99</v>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>43033-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>66813</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Seria 28 – Zwierzęta – sześciopak</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Minifigurki</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="F48" s="6" t="n"/>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>brak - GWP lub cena nieogloszona</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>66813-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>72050</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Mario Kart - Luigi i Mach 8</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>Super Mario</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>2234</v>
-      </c>
-      <c r="F49" s="12" t="n">
-        <v>779.99</v>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>karta Piotra</t>
-        </is>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>/zestaw/72050/</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>brak ceny katalogowej</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>uzupelnic cene katalogowa - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>72050-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>72052</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Mario wskakujący do rury</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Super Mario</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>41.99</v>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>72052-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>72054</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Mario Kart™ – wyścigi z Mario</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Super Mario</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>84</v>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>62.99</v>
-      </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>72054-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>72055</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Przygody Mario na plaży</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Super Mario</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>196</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>84.98999999999999</v>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>72055-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>72056</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Mario Kart™ – Luigi i Bowser Jr. na wyścigu</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Super Mario</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E53" s="11" t="n">
-        <v>104</v>
-      </c>
-      <c r="F53" s="12" t="n">
-        <v>126.99</v>
-      </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>72056-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>72057</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Yoshi w domu Mario</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Super Mario</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>147</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>174.99</v>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
-        <is>
-          <t>72057-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>72058</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Mario Kart™ – Bowser i waleczny wyścig</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Super Mario</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E55" s="11" t="n">
-        <v>409</v>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>259.99</v>
-      </c>
-      <c r="G55" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>72058-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>72060</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Fire Mario i Bowser na zamku</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>LEGO Super Mario</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>850</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>429.99</v>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
-        <is>
-          <t>72060-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>72061</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>Fire Luigi kontra Koopa Troopa – bitwa</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>LEGO Super Mario</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v>241</v>
-      </c>
-      <c r="F57" s="12" t="n">
-        <v>126.99</v>
-      </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
           <t>72061-1</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>76330</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Logo Batmana™</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>LEGO DC / Batman</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>678</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>339.99</v>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>76330-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>76331</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>Batmobil™ z filmu Batman v Superman™</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>LEGO DC / Batman</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v>220</v>
-      </c>
-      <c r="F59" s="12" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="G59" s="10" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K59" s="13" t="inlineStr">
-        <is>
-          <t>76331-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>76333</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Batmobil™ z filmu Batman i Robin™</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>LEGO DC / Batman</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>272</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>rejestr RRP</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>brak w katalogu serwisu</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>dopisac do katalog.json (nazwa, rok, seria, cena) - wtedy wejdzie do kolejki</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>76333-1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K60"/>
+  <autoFilter ref="A1:K36"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
